--- a/myprojects/GatiGo/GatiGo_CVP_BreakEven.xlsx
+++ b/myprojects/GatiGo/GatiGo_CVP_BreakEven.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inanj\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inanj\Documents\GitHub\inakm.github.io\myprojects\GatiGo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0812390-7993-4504-A118-94996E5BBDDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B265DF7-1B35-4E8C-9A2B-E618E2E51EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -608,8 +608,8 @@
     <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\);\-"/>
     <numFmt numFmtId="169" formatCode="0.0%;\(0.0%\);\-"/>
-    <numFmt numFmtId="171" formatCode="0%;\(0%\);\-"/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;\ * #,##0_ ;_ &quot;₹&quot;\ * \-#,##0_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="170" formatCode="0%;\(0%\);\-"/>
+    <numFmt numFmtId="171" formatCode="_ &quot;₹&quot;\ * #,##0_ ;_ &quot;₹&quot;\ * \-#,##0_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="38" x14ac:knownFonts="1">
     <font>
@@ -1049,44 +1049,8 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1289,121 +1253,156 @@
     <xf numFmtId="166" fontId="21" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="14" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="15" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="30" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="13" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="34" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="18" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="36" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="36" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="14" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="15" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="29" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="30" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="34" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="18" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="36" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="36" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3272,315 +3271,315 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="101" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
     </row>
     <row r="2" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="90" t="s">
+      <c r="A3" s="103" t="s">
         <v>178</v>
       </c>
-      <c r="B3" s="90"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="6">
         <f>'CVP Inputs'!B7</f>
         <v>19.067796610169491</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="6">
         <f>'Scenario Analysis'!C11</f>
         <v>19.067796610169491</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="6">
         <f>'Scenario Analysis'!D11</f>
         <v>20.974576271186443</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="6">
         <f>'Scenario Analysis'!F11</f>
         <v>17.161016949152543</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="6">
         <f>'CVP Inputs'!B12</f>
         <v>54.5</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="6">
         <f>'Scenario Analysis'!C12</f>
         <v>59.95</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="6">
         <f>'Scenario Analysis'!D12</f>
         <v>54.5</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="6">
         <f>'Scenario Analysis'!F12</f>
         <v>59.95</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="6">
         <f>'CVP Inputs'!B14</f>
         <v>-35.432203389830505</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="6">
         <f>'Scenario Analysis'!C13</f>
         <v>-40.882203389830508</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="6">
         <f>'Scenario Analysis'!D13</f>
         <v>-33.525423728813557</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="6">
         <f>'Scenario Analysis'!F13</f>
         <v>-42.788983050847463</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="7">
         <f>'CVP Inputs'!B15</f>
         <v>-1.858222222222222</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="7">
         <f>'Scenario Analysis'!C14</f>
         <v>-2.1440444444444444</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="7">
         <f>'Scenario Analysis'!D14</f>
         <v>-1.598383838383838</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="7">
         <f>'Scenario Analysis'!F14</f>
         <v>-2.4933827160493829</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="8">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="8">
         <f>'Scenario Analysis'!C9</f>
         <v>469000</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="8">
         <f>'Scenario Analysis'!D9</f>
         <v>469000</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="8">
         <f>'Scenario Analysis'!F9</f>
         <v>469000</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+      <c r="B10" s="104"/>
+      <c r="C10" s="104"/>
+      <c r="D10" s="104"/>
+      <c r="E10" s="104"/>
     </row>
     <row r="11" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="10">
         <f>'Break-Even Analysis'!B10</f>
         <v>-13236.546280794069</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="10">
         <f>'Scenario Analysis'!C16</f>
         <v>-11471.984411600091</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="10">
         <f>'Scenario Analysis'!D16</f>
         <v>-13989.38321536906</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="10">
         <f>'Scenario Analysis'!F16</f>
         <v>-10960.765284902258</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="22">
+      <c r="B12" s="10">
         <f>'Break-Even Analysis'!B11</f>
         <v>-441.2182093598023</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="10">
         <f>'Scenario Analysis'!C17</f>
         <v>-382.39948038666972</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="10">
         <f>'Scenario Analysis'!D17</f>
         <v>-466.31277384563532</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="10">
         <f>'Scenario Analysis'!F17</f>
         <v>-365.35884283007528</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B13" s="11">
         <f>'Break-Even Analysis'!B12</f>
         <v>-252391.77230327675</v>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="11">
         <f>'Scenario Analysis'!C18</f>
         <v>-218745.46547542547</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="11">
         <f>'Scenario Analysis'!D18</f>
         <v>-293421.38523761381</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="11">
         <f>'Scenario Analysis'!F18</f>
         <v>-188097.87882989045</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="105"/>
+      <c r="D14" s="105"/>
+      <c r="E14" s="105"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="12">
         <f>'Break-Even Analysis'!B15</f>
         <v>5980</v>
       </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="12">
         <f>'Break-Even Analysis'!B17</f>
         <v>19216.546280794071</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="8">
         <f>'Break-Even Analysis'!B18</f>
         <v>366417.19603209035</v>
       </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="14">
         <f>'Break-Even Analysis'!B19</f>
         <v>3.2134692777247609</v>
       </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="15">
         <f>'Break-Even Analysis'!B20</f>
         <v>0.31119015418377738</v>
       </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="84"/>
-      <c r="B20" s="84"/>
-      <c r="C20" s="84"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84"/>
+      <c r="A20" s="100"/>
+      <c r="B20" s="100"/>
+      <c r="C20" s="100"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="100"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="84"/>
-      <c r="B21" s="84"/>
-      <c r="C21" s="84"/>
-      <c r="D21" s="84"/>
-      <c r="E21" s="84"/>
+      <c r="A21" s="100"/>
+      <c r="B21" s="100"/>
+      <c r="C21" s="100"/>
+      <c r="D21" s="100"/>
+      <c r="E21" s="100"/>
     </row>
     <row r="23" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="83" t="s">
+      <c r="A23" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="B23" s="82"/>
-      <c r="C23" s="82"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="82" t="s">
+      <c r="B23" s="69"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3611,405 +3610,405 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="111" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
+      <c r="A2" s="113"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="39">
+      <c r="B4" s="27">
         <v>150</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="95" t="s">
+      <c r="D4" s="71" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="96">
+      <c r="B5" s="72">
         <v>0.15</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="17" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="96">
+      <c r="B6" s="72">
         <v>0.18</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="18">
         <f>B4*B5/(1+B6)</f>
         <v>19.067796610169491</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="20" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="97" t="s">
+      <c r="A8" s="106" t="s">
         <v>148</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="39">
+      <c r="B9" s="27">
         <v>50</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="D9" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="39">
+      <c r="B10" s="27">
         <v>3</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="95" t="s">
+      <c r="D10" s="71" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="27">
         <v>1.5</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="98">
+      <c r="E11" s="73">
         <f>(62000/15460)/2</f>
         <v>2.0051746442432083</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="99">
+      <c r="B12" s="74">
         <f>B9+B10+B11</f>
         <v>54.5</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="107" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="107"/>
+      <c r="D13" s="107"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="102">
+      <c r="B14" s="76">
         <f>B7-B12</f>
         <v>-35.432203389830505</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="100" t="s">
+      <c r="D14" s="75" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="103">
+      <c r="B15" s="77">
         <f>B14/B7</f>
         <v>-1.858222222222222</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="26" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="97" t="s">
+      <c r="A16" s="106" t="s">
         <v>151</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
+      <c r="B16" s="107"/>
+      <c r="C16" s="107"/>
+      <c r="D16" s="107"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="39">
+      <c r="B17" s="27">
         <v>120000</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="D17" s="17" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="39">
+      <c r="B18" s="27">
         <v>80000</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="17" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="39">
+      <c r="B19" s="27">
         <v>60000</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="D19" s="17" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="39">
+      <c r="B20" s="27">
         <v>35000</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="D20" s="17" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="39">
+      <c r="B21" s="27">
         <v>25000</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="17" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="39">
+      <c r="B22" s="27">
         <v>80000</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="29" t="s">
+      <c r="D22" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="39">
+      <c r="B23" s="27">
         <v>15000</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="29" t="s">
+      <c r="D23" s="17" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="39">
+      <c r="B24" s="27">
         <v>10000</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B25" s="39">
+      <c r="B25" s="27">
         <v>15000</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="39">
+      <c r="B26" s="27">
         <v>8000</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="29" t="s">
+      <c r="D26" s="17" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="39">
+      <c r="B27" s="27">
         <v>5000</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D27" s="29" t="s">
+      <c r="D27" s="17" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="39">
+      <c r="B28" s="27">
         <v>3500</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="17" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="39">
+      <c r="B29" s="27">
         <v>12500</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="29" t="s">
+      <c r="D29" s="17" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B30" s="40">
+      <c r="B30" s="28">
         <f>SUM(B17:B29)</f>
         <v>469000</v>
       </c>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="20" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="85" t="s">
+      <c r="A32" s="108" t="s">
         <v>145</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="6" t="s">
+      <c r="B32" s="109"/>
+      <c r="C32" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="6"/>
+      <c r="D32" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4039,359 +4038,359 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="111" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="101" t="s">
+      <c r="A3" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="8">
         <f>'CVP Inputs'!B7</f>
         <v>19.067796610169491</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="17" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="8">
         <f>'CVP Inputs'!B12</f>
         <v>54.5</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="17" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="104">
+      <c r="B6" s="78">
         <f>B4-B5</f>
         <v>-35.432203389830505</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="20" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="105">
+      <c r="B7" s="79">
         <f>B6/B4</f>
         <v>-1.858222222222222</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="17" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="11">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="20" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="105" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
+      <c r="B9" s="105"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="43">
+      <c r="B10" s="31">
         <f>B8/B6</f>
         <v>-13236.546280794069</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="106" t="s">
+      <c r="D10" s="80" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="44">
+      <c r="B11" s="32">
         <f>B10/30</f>
         <v>-441.2182093598023</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="106" t="s">
+      <c r="D11" s="80" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="28">
         <f>B10*B4</f>
         <v>-252391.77230327675</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="20" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="46">
+      <c r="B13" s="34">
         <f>IFERROR(B8/B7,0)</f>
         <v>-252391.77230327675</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="107" t="s">
+      <c r="D13" s="81" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="116" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+      <c r="B14" s="116"/>
+      <c r="C14" s="116"/>
+      <c r="D14" s="116"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="48">
+      <c r="B15" s="36">
         <v>5980</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="95" t="s">
+      <c r="D15" s="71" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="49">
+      <c r="B16" s="37">
         <f>B15*B4</f>
         <v>114025.42372881356</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="29" t="s">
+      <c r="D16" s="17" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="43">
+      <c r="B17" s="31">
         <f>B15-B10</f>
         <v>19216.546280794071</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="106" t="s">
+      <c r="D17" s="80" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="40">
+      <c r="B18" s="28">
         <f>B16-B12</f>
         <v>366417.19603209035</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="20" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="108">
+      <c r="B19" s="82">
         <f>IFERROR((B15-B10)/B15,0)</f>
         <v>3.2134692777247609</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="20" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="51">
+      <c r="B20" s="39">
         <f>IFERROR(B15*B6/(B15*B6-B8),0)</f>
         <v>0.31119015418377738</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="47" t="s">
+      <c r="D20" s="35" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="107" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="107"/>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B22" s="49">
+      <c r="B22" s="37">
         <f>B15*B4</f>
         <v>114025.42372881356</v>
       </c>
-      <c r="C22" s="42" t="s">
+      <c r="C22" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="29" t="s">
+      <c r="D22" s="17" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B23" s="49">
+      <c r="B23" s="37">
         <f>B15*B5</f>
         <v>325910</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="29" t="s">
+      <c r="D23" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B24" s="52">
+      <c r="B24" s="40">
         <f>B22-B23</f>
         <v>-211884.57627118644</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="20" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="8">
         <f>B8</f>
         <v>469000</v>
       </c>
-      <c r="C25" s="42" t="s">
+      <c r="C25" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="17" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B26" s="40">
+      <c r="B26" s="28">
         <f>B24-B25</f>
         <v>-680884.57627118647</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="106" t="s">
+      <c r="D26" s="80" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="85" t="s">
+      <c r="A28" s="108" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="6" t="s">
+      <c r="B28" s="109"/>
+      <c r="C28" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="6"/>
+      <c r="D28" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4425,1284 +4424,1284 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="117" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="110" t="s">
+      <c r="A3" s="83" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="83" t="s">
         <v>162</v>
       </c>
-      <c r="C3" s="110" t="s">
+      <c r="C3" s="83" t="s">
         <v>163</v>
       </c>
-      <c r="D3" s="110" t="s">
+      <c r="D3" s="83" t="s">
         <v>164</v>
       </c>
-      <c r="E3" s="110" t="s">
+      <c r="E3" s="83" t="s">
         <v>165</v>
       </c>
-      <c r="F3" s="110" t="s">
+      <c r="F3" s="83" t="s">
         <v>166</v>
       </c>
-      <c r="G3" s="110" t="s">
+      <c r="G3" s="83" t="s">
         <v>167</v>
       </c>
-      <c r="H3" s="110" t="s">
+      <c r="H3" s="83" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="53">
+      <c r="A4" s="41">
         <v>1000</v>
       </c>
-      <c r="B4" s="49">
+      <c r="B4" s="37">
         <f>A4*'CVP Inputs'!B7</f>
         <v>19067.796610169491</v>
       </c>
-      <c r="C4" s="49">
+      <c r="C4" s="37">
         <f>A4*'CVP Inputs'!B12</f>
         <v>54500</v>
       </c>
-      <c r="D4" s="54">
+      <c r="D4" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E4" s="49">
+      <c r="E4" s="37">
         <f>C4+D4</f>
         <v>523500</v>
       </c>
-      <c r="F4" s="55">
+      <c r="F4" s="43">
         <f>B4-E4</f>
         <v>-504432.20338983054</v>
       </c>
-      <c r="G4" s="49">
+      <c r="G4" s="37">
         <f>A4*'CVP Inputs'!B14</f>
         <v>-35432.203389830502</v>
       </c>
-      <c r="H4" s="56" t="str">
+      <c r="H4" s="44" t="str">
         <f>IF(F4&gt;=0,"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="53">
+      <c r="A5" s="41">
         <v>2000</v>
       </c>
-      <c r="B5" s="49">
+      <c r="B5" s="37">
         <f>A5*'CVP Inputs'!B7</f>
         <v>38135.593220338982</v>
       </c>
-      <c r="C5" s="49">
+      <c r="C5" s="37">
         <f>A5*'CVP Inputs'!B12</f>
         <v>109000</v>
       </c>
-      <c r="D5" s="54">
+      <c r="D5" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E5" s="49">
-        <f t="shared" ref="E4:E40" si="0">C5+D5</f>
+      <c r="E5" s="37">
+        <f t="shared" ref="E5:E40" si="0">C5+D5</f>
         <v>578000</v>
       </c>
-      <c r="F5" s="55">
-        <f t="shared" ref="F4:F40" si="1">B5-E5</f>
+      <c r="F5" s="43">
+        <f t="shared" ref="F5:F40" si="1">B5-E5</f>
         <v>-539864.40677966108</v>
       </c>
-      <c r="G5" s="49">
+      <c r="G5" s="37">
         <f>A5*'CVP Inputs'!B14</f>
         <v>-70864.406779661003</v>
       </c>
-      <c r="H5" s="56" t="str">
+      <c r="H5" s="44" t="str">
         <f>IF(F5&gt;=0,"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="53">
+      <c r="A6" s="41">
         <v>3000</v>
       </c>
-      <c r="B6" s="49">
+      <c r="B6" s="37">
         <f>A6*'CVP Inputs'!B7</f>
         <v>57203.389830508473</v>
       </c>
-      <c r="C6" s="49">
+      <c r="C6" s="37">
         <f>A6*'CVP Inputs'!B12</f>
         <v>163500</v>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="37">
         <f t="shared" si="0"/>
         <v>632500</v>
       </c>
-      <c r="F6" s="55">
+      <c r="F6" s="43">
         <f t="shared" si="1"/>
         <v>-575296.6101694915</v>
       </c>
-      <c r="G6" s="49">
+      <c r="G6" s="37">
         <f>A6*'CVP Inputs'!B14</f>
         <v>-106296.61016949151</v>
       </c>
-      <c r="H6" s="56" t="str">
+      <c r="H6" s="44" t="str">
         <f>IF(F6&gt;=0,"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="53">
+      <c r="A7" s="41">
         <v>4000</v>
       </c>
-      <c r="B7" s="49">
+      <c r="B7" s="37">
         <f>A7*'CVP Inputs'!B7</f>
         <v>76271.186440677964</v>
       </c>
-      <c r="C7" s="49">
+      <c r="C7" s="37">
         <f>A7*'CVP Inputs'!B12</f>
         <v>218000</v>
       </c>
-      <c r="D7" s="54">
+      <c r="D7" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="37">
         <f t="shared" si="0"/>
         <v>687000</v>
       </c>
-      <c r="F7" s="55">
+      <c r="F7" s="43">
         <f t="shared" si="1"/>
         <v>-610728.81355932204</v>
       </c>
-      <c r="G7" s="49">
+      <c r="G7" s="37">
         <f>A7*'CVP Inputs'!B14</f>
         <v>-141728.81355932201</v>
       </c>
-      <c r="H7" s="56" t="str">
+      <c r="H7" s="44" t="str">
         <f>IF(F7&gt;=0,"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="57">
+      <c r="A8" s="45">
         <v>4680</v>
       </c>
-      <c r="B8" s="58">
+      <c r="B8" s="46">
         <f>A8*'CVP Inputs'!B7</f>
         <v>89237.288135593219</v>
       </c>
-      <c r="C8" s="58">
+      <c r="C8" s="46">
         <f>A8*'CVP Inputs'!B12</f>
         <v>255060</v>
       </c>
-      <c r="D8" s="59">
+      <c r="D8" s="47">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E8" s="58">
+      <c r="E8" s="46">
         <f t="shared" si="0"/>
         <v>724060</v>
       </c>
-      <c r="F8" s="60">
+      <c r="F8" s="48">
         <f t="shared" si="1"/>
         <v>-634822.71186440683</v>
       </c>
-      <c r="G8" s="58">
+      <c r="G8" s="46">
         <f>A8*'CVP Inputs'!B14</f>
         <v>-165822.71186440677</v>
       </c>
-      <c r="H8" s="61" t="s">
+      <c r="H8" s="49" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="57">
+      <c r="A9" s="45">
         <v>4800</v>
       </c>
-      <c r="B9" s="58">
+      <c r="B9" s="46">
         <f>A9*'CVP Inputs'!B7</f>
         <v>91525.423728813563</v>
       </c>
-      <c r="C9" s="58">
+      <c r="C9" s="46">
         <f>A9*'CVP Inputs'!B12</f>
         <v>261600</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="47">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E9" s="58">
+      <c r="E9" s="46">
         <f t="shared" si="0"/>
         <v>730600</v>
       </c>
-      <c r="F9" s="60">
+      <c r="F9" s="48">
         <f t="shared" si="1"/>
         <v>-639074.57627118647</v>
       </c>
-      <c r="G9" s="58">
+      <c r="G9" s="46">
         <f>A9*'CVP Inputs'!B14</f>
         <v>-170074.57627118644</v>
       </c>
-      <c r="H9" s="61" t="s">
+      <c r="H9" s="49" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="53">
+      <c r="A10" s="41">
         <v>5000</v>
       </c>
-      <c r="B10" s="49">
+      <c r="B10" s="37">
         <f>A10*'CVP Inputs'!B7</f>
         <v>95338.983050847455</v>
       </c>
-      <c r="C10" s="49">
+      <c r="C10" s="37">
         <f>A10*'CVP Inputs'!B12</f>
         <v>272500</v>
       </c>
-      <c r="D10" s="54">
+      <c r="D10" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E10" s="49">
+      <c r="E10" s="37">
         <f t="shared" si="0"/>
         <v>741500</v>
       </c>
-      <c r="F10" s="55">
+      <c r="F10" s="43">
         <f t="shared" si="1"/>
         <v>-646161.01694915257</v>
       </c>
-      <c r="G10" s="49">
+      <c r="G10" s="37">
         <f>A10*'CVP Inputs'!B14</f>
         <v>-177161.01694915252</v>
       </c>
-      <c r="H10" s="56" t="str">
+      <c r="H10" s="44" t="str">
         <f>IF(F10&gt;=0,"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="57">
+      <c r="A11" s="45">
         <v>5980</v>
       </c>
-      <c r="B11" s="58">
+      <c r="B11" s="46">
         <f>A11*'CVP Inputs'!B7</f>
         <v>114025.42372881356</v>
       </c>
-      <c r="C11" s="58">
+      <c r="C11" s="46">
         <f>A11*'CVP Inputs'!B12</f>
         <v>325910</v>
       </c>
-      <c r="D11" s="59">
+      <c r="D11" s="47">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E11" s="58">
+      <c r="E11" s="46">
         <f t="shared" si="0"/>
         <v>794910</v>
       </c>
-      <c r="F11" s="60">
+      <c r="F11" s="48">
         <f t="shared" si="1"/>
         <v>-680884.57627118647</v>
       </c>
-      <c r="G11" s="58">
+      <c r="G11" s="46">
         <f>A11*'CVP Inputs'!B14</f>
         <v>-211884.57627118641</v>
       </c>
-      <c r="H11" s="61" t="s">
+      <c r="H11" s="49" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="53">
+      <c r="A12" s="41">
         <v>6000</v>
       </c>
-      <c r="B12" s="49">
+      <c r="B12" s="37">
         <f>A12*'CVP Inputs'!B7</f>
         <v>114406.77966101695</v>
       </c>
-      <c r="C12" s="49">
+      <c r="C12" s="37">
         <f>A12*'CVP Inputs'!B12</f>
         <v>327000</v>
       </c>
-      <c r="D12" s="54">
+      <c r="D12" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="37">
         <f t="shared" si="0"/>
         <v>796000</v>
       </c>
-      <c r="F12" s="55">
+      <c r="F12" s="43">
         <f t="shared" si="1"/>
         <v>-681593.220338983</v>
       </c>
-      <c r="G12" s="49">
+      <c r="G12" s="37">
         <f>A12*'CVP Inputs'!B14</f>
         <v>-212593.22033898302</v>
       </c>
-      <c r="H12" s="56" t="str">
+      <c r="H12" s="44" t="str">
         <f t="shared" ref="H12:H40" si="2">IF(F12&gt;=0,"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="53">
+      <c r="A13" s="41">
         <v>7000</v>
       </c>
-      <c r="B13" s="49">
+      <c r="B13" s="37">
         <f>A13*'CVP Inputs'!B7</f>
         <v>133474.57627118644</v>
       </c>
-      <c r="C13" s="49">
+      <c r="C13" s="37">
         <f>A13*'CVP Inputs'!B12</f>
         <v>381500</v>
       </c>
-      <c r="D13" s="54">
+      <c r="D13" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E13" s="49">
+      <c r="E13" s="37">
         <f t="shared" si="0"/>
         <v>850500</v>
       </c>
-      <c r="F13" s="55">
+      <c r="F13" s="43">
         <f t="shared" si="1"/>
         <v>-717025.42372881353</v>
       </c>
-      <c r="G13" s="49">
+      <c r="G13" s="37">
         <f>A13*'CVP Inputs'!B14</f>
         <v>-248025.42372881353</v>
       </c>
-      <c r="H13" s="56" t="str">
+      <c r="H13" s="44" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="53">
+      <c r="A14" s="41">
         <v>8000</v>
       </c>
-      <c r="B14" s="49">
+      <c r="B14" s="37">
         <f>A14*'CVP Inputs'!B7</f>
         <v>152542.37288135593</v>
       </c>
-      <c r="C14" s="49">
+      <c r="C14" s="37">
         <f>A14*'CVP Inputs'!B12</f>
         <v>436000</v>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E14" s="49">
+      <c r="E14" s="37">
         <f t="shared" si="0"/>
         <v>905000</v>
       </c>
-      <c r="F14" s="55">
+      <c r="F14" s="43">
         <f t="shared" si="1"/>
         <v>-752457.62711864407</v>
       </c>
-      <c r="G14" s="49">
+      <c r="G14" s="37">
         <f>A14*'CVP Inputs'!B14</f>
         <v>-283457.62711864401</v>
       </c>
-      <c r="H14" s="56" t="str">
+      <c r="H14" s="44" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="53">
+      <c r="A15" s="41">
         <v>9000</v>
       </c>
-      <c r="B15" s="49">
+      <c r="B15" s="37">
         <f>A15*'CVP Inputs'!B7</f>
         <v>171610.16949152542</v>
       </c>
-      <c r="C15" s="49">
+      <c r="C15" s="37">
         <f>A15*'CVP Inputs'!B12</f>
         <v>490500</v>
       </c>
-      <c r="D15" s="54">
+      <c r="D15" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="37">
         <f t="shared" si="0"/>
         <v>959500</v>
       </c>
-      <c r="F15" s="55">
+      <c r="F15" s="43">
         <f t="shared" si="1"/>
         <v>-787889.83050847461</v>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="37">
         <f>A15*'CVP Inputs'!B14</f>
         <v>-318889.83050847455</v>
       </c>
-      <c r="H15" s="56" t="str">
+      <c r="H15" s="44" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="53">
+      <c r="A16" s="41">
         <v>10000</v>
       </c>
-      <c r="B16" s="49">
+      <c r="B16" s="37">
         <f>A16*'CVP Inputs'!B7</f>
         <v>190677.96610169491</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>A16*'CVP Inputs'!B12</f>
         <v>545000</v>
       </c>
-      <c r="D16" s="54">
+      <c r="D16" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="37">
         <f t="shared" si="0"/>
         <v>1014000</v>
       </c>
-      <c r="F16" s="55">
+      <c r="F16" s="43">
         <f t="shared" si="1"/>
         <v>-823322.03389830515</v>
       </c>
-      <c r="G16" s="49">
+      <c r="G16" s="37">
         <f>A16*'CVP Inputs'!B14</f>
         <v>-354322.03389830503</v>
       </c>
-      <c r="H16" s="56" t="str">
+      <c r="H16" s="44" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="53">
+      <c r="A17" s="41">
         <v>11000</v>
       </c>
-      <c r="B17" s="49">
+      <c r="B17" s="37">
         <f>A17*'CVP Inputs'!B7</f>
         <v>209745.7627118644</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>A17*'CVP Inputs'!B12</f>
         <v>599500</v>
       </c>
-      <c r="D17" s="54">
+      <c r="D17" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="37">
         <f t="shared" si="0"/>
         <v>1068500</v>
       </c>
-      <c r="F17" s="55">
+      <c r="F17" s="43">
         <f t="shared" si="1"/>
         <v>-858754.23728813557</v>
       </c>
-      <c r="G17" s="49">
+      <c r="G17" s="37">
         <f>A17*'CVP Inputs'!B14</f>
         <v>-389754.23728813557</v>
       </c>
-      <c r="H17" s="56" t="str">
+      <c r="H17" s="44" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="53">
+      <c r="A18" s="41">
         <v>12000</v>
       </c>
-      <c r="B18" s="49">
+      <c r="B18" s="37">
         <f>A18*'CVP Inputs'!B7</f>
         <v>228813.55932203389</v>
       </c>
-      <c r="C18" s="49">
+      <c r="C18" s="37">
         <f>A18*'CVP Inputs'!B12</f>
         <v>654000</v>
       </c>
-      <c r="D18" s="54">
+      <c r="D18" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="37">
         <f t="shared" si="0"/>
         <v>1123000</v>
       </c>
-      <c r="F18" s="112">
+      <c r="F18" s="84">
         <f t="shared" si="1"/>
         <v>-894186.44067796611</v>
       </c>
-      <c r="G18" s="49">
+      <c r="G18" s="37">
         <f>A18*'CVP Inputs'!B14</f>
         <v>-425186.44067796605</v>
       </c>
-      <c r="H18" s="113" t="str">
+      <c r="H18" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="53">
+      <c r="A19" s="41">
         <v>13000</v>
       </c>
-      <c r="B19" s="49">
+      <c r="B19" s="37">
         <f>A19*'CVP Inputs'!B7</f>
         <v>247881.35593220338</v>
       </c>
-      <c r="C19" s="49">
+      <c r="C19" s="37">
         <f>A19*'CVP Inputs'!B12</f>
         <v>708500</v>
       </c>
-      <c r="D19" s="54">
+      <c r="D19" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E19" s="49">
+      <c r="E19" s="37">
         <f t="shared" si="0"/>
         <v>1177500</v>
       </c>
-      <c r="F19" s="112">
+      <c r="F19" s="84">
         <f t="shared" si="1"/>
         <v>-929618.64406779665</v>
       </c>
-      <c r="G19" s="49">
+      <c r="G19" s="37">
         <f>A19*'CVP Inputs'!B14</f>
         <v>-460618.64406779659</v>
       </c>
-      <c r="H19" s="113" t="str">
+      <c r="H19" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="53">
+      <c r="A20" s="41">
         <v>14000</v>
       </c>
-      <c r="B20" s="49">
+      <c r="B20" s="37">
         <f>A20*'CVP Inputs'!B7</f>
         <v>266949.15254237287</v>
       </c>
-      <c r="C20" s="49">
+      <c r="C20" s="37">
         <f>A20*'CVP Inputs'!B12</f>
         <v>763000</v>
       </c>
-      <c r="D20" s="54">
+      <c r="D20" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E20" s="49">
+      <c r="E20" s="37">
         <f t="shared" si="0"/>
         <v>1232000</v>
       </c>
-      <c r="F20" s="112">
+      <c r="F20" s="84">
         <f t="shared" si="1"/>
         <v>-965050.84745762707</v>
       </c>
-      <c r="G20" s="49">
+      <c r="G20" s="37">
         <f>A20*'CVP Inputs'!B14</f>
         <v>-496050.84745762707</v>
       </c>
-      <c r="H20" s="113" t="str">
+      <c r="H20" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="53">
+      <c r="A21" s="41">
         <v>15000</v>
       </c>
-      <c r="B21" s="49">
+      <c r="B21" s="37">
         <f>A21*'CVP Inputs'!B7</f>
         <v>286016.94915254239</v>
       </c>
-      <c r="C21" s="49">
+      <c r="C21" s="37">
         <f>A21*'CVP Inputs'!B12</f>
         <v>817500</v>
       </c>
-      <c r="D21" s="54">
+      <c r="D21" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E21" s="49">
+      <c r="E21" s="37">
         <f t="shared" si="0"/>
         <v>1286500</v>
       </c>
-      <c r="F21" s="112">
+      <c r="F21" s="84">
         <f t="shared" si="1"/>
         <v>-1000483.0508474576</v>
       </c>
-      <c r="G21" s="49">
+      <c r="G21" s="37">
         <f>A21*'CVP Inputs'!B14</f>
         <v>-531483.05084745761</v>
       </c>
-      <c r="H21" s="113" t="str">
+      <c r="H21" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="53">
+      <c r="A22" s="41">
         <v>16000</v>
       </c>
-      <c r="B22" s="49">
+      <c r="B22" s="37">
         <f>A22*'CVP Inputs'!B7</f>
         <v>305084.74576271186</v>
       </c>
-      <c r="C22" s="49">
+      <c r="C22" s="37">
         <f>A22*'CVP Inputs'!B12</f>
         <v>872000</v>
       </c>
-      <c r="D22" s="54">
+      <c r="D22" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E22" s="49">
+      <c r="E22" s="37">
         <f t="shared" si="0"/>
         <v>1341000</v>
       </c>
-      <c r="F22" s="112">
+      <c r="F22" s="84">
         <f t="shared" si="1"/>
         <v>-1035915.2542372881</v>
       </c>
-      <c r="G22" s="49">
+      <c r="G22" s="37">
         <f>A22*'CVP Inputs'!B14</f>
         <v>-566915.25423728803</v>
       </c>
-      <c r="H22" s="113" t="str">
+      <c r="H22" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="53">
+      <c r="A23" s="41">
         <v>18000</v>
       </c>
-      <c r="B23" s="49">
+      <c r="B23" s="37">
         <f>A23*'CVP Inputs'!B7</f>
         <v>343220.33898305084</v>
       </c>
-      <c r="C23" s="49">
+      <c r="C23" s="37">
         <f>A23*'CVP Inputs'!B12</f>
         <v>981000</v>
       </c>
-      <c r="D23" s="54">
+      <c r="D23" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E23" s="49">
+      <c r="E23" s="37">
         <f t="shared" si="0"/>
         <v>1450000</v>
       </c>
-      <c r="F23" s="112">
+      <c r="F23" s="84">
         <f t="shared" si="1"/>
         <v>-1106779.6610169492</v>
       </c>
-      <c r="G23" s="49">
+      <c r="G23" s="37">
         <f>A23*'CVP Inputs'!B14</f>
         <v>-637779.6610169491</v>
       </c>
-      <c r="H23" s="113" t="str">
+      <c r="H23" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="53">
+      <c r="A24" s="41">
         <v>20000</v>
       </c>
-      <c r="B24" s="49">
+      <c r="B24" s="37">
         <f>A24*'CVP Inputs'!B7</f>
         <v>381355.93220338982</v>
       </c>
-      <c r="C24" s="49">
+      <c r="C24" s="37">
         <f>A24*'CVP Inputs'!B12</f>
         <v>1090000</v>
       </c>
-      <c r="D24" s="54">
+      <c r="D24" s="42">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E24" s="49">
+      <c r="E24" s="37">
         <f t="shared" si="0"/>
         <v>1559000</v>
       </c>
-      <c r="F24" s="112">
+      <c r="F24" s="84">
         <f t="shared" si="1"/>
         <v>-1177644.0677966103</v>
       </c>
-      <c r="G24" s="49">
+      <c r="G24" s="37">
         <f>A24*'CVP Inputs'!B14</f>
         <v>-708644.06779661006</v>
       </c>
-      <c r="H24" s="113" t="str">
+      <c r="H24" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="53">
+      <c r="A25" s="41">
         <v>25000</v>
       </c>
-      <c r="B25" s="49">
+      <c r="B25" s="37">
         <f>A25*'CVP Inputs'!$B$7</f>
         <v>476694.9152542373</v>
       </c>
-      <c r="C25" s="49">
+      <c r="C25" s="37">
         <f>A25*'CVP Inputs'!$B$12</f>
         <v>1362500</v>
       </c>
-      <c r="D25" s="54">
+      <c r="D25" s="42">
         <f>'CVP Inputs'!$B$30</f>
         <v>469000</v>
       </c>
-      <c r="E25" s="49">
+      <c r="E25" s="37">
         <f t="shared" si="0"/>
         <v>1831500</v>
       </c>
-      <c r="F25" s="112">
+      <c r="F25" s="84">
         <f t="shared" si="1"/>
         <v>-1354805.0847457626</v>
       </c>
-      <c r="G25" s="49">
+      <c r="G25" s="37">
         <f>A25*'CVP Inputs'!$B$14</f>
         <v>-885805.08474576264</v>
       </c>
-      <c r="H25" s="113" t="str">
+      <c r="H25" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="53">
+      <c r="A26" s="41">
         <v>30000</v>
       </c>
-      <c r="B26" s="49">
+      <c r="B26" s="37">
         <f>A26*'CVP Inputs'!$B$7</f>
         <v>572033.89830508479</v>
       </c>
-      <c r="C26" s="49">
+      <c r="C26" s="37">
         <f>A26*'CVP Inputs'!$B$12</f>
         <v>1635000</v>
       </c>
-      <c r="D26" s="54">
+      <c r="D26" s="42">
         <f>'CVP Inputs'!$B$30</f>
         <v>469000</v>
       </c>
-      <c r="E26" s="49">
+      <c r="E26" s="37">
         <f t="shared" si="0"/>
         <v>2104000</v>
       </c>
-      <c r="F26" s="112">
+      <c r="F26" s="84">
         <f t="shared" si="1"/>
         <v>-1531966.1016949152</v>
       </c>
-      <c r="G26" s="49">
+      <c r="G26" s="37">
         <f>A26*'CVP Inputs'!$B$14</f>
         <v>-1062966.1016949152</v>
       </c>
-      <c r="H26" s="113" t="str">
+      <c r="H26" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="53">
+      <c r="A27" s="41">
         <v>40000</v>
       </c>
-      <c r="B27" s="49">
+      <c r="B27" s="37">
         <f>A27*'CVP Inputs'!$B$7</f>
         <v>762711.86440677964</v>
       </c>
-      <c r="C27" s="49">
+      <c r="C27" s="37">
         <f>A27*'CVP Inputs'!$B$12</f>
         <v>2180000</v>
       </c>
-      <c r="D27" s="54">
+      <c r="D27" s="42">
         <f>'CVP Inputs'!$B$30</f>
         <v>469000</v>
       </c>
-      <c r="E27" s="49">
+      <c r="E27" s="37">
         <f t="shared" si="0"/>
         <v>2649000</v>
       </c>
-      <c r="F27" s="112">
+      <c r="F27" s="84">
         <f t="shared" si="1"/>
         <v>-1886288.1355932204</v>
       </c>
-      <c r="G27" s="49">
+      <c r="G27" s="37">
         <f>A27*'CVP Inputs'!$B$14</f>
         <v>-1417288.1355932201</v>
       </c>
-      <c r="H27" s="113" t="str">
+      <c r="H27" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="53">
+      <c r="A28" s="41">
         <v>50000</v>
       </c>
-      <c r="B28" s="49">
+      <c r="B28" s="37">
         <f>A28*'CVP Inputs'!$B$7</f>
         <v>953389.83050847461</v>
       </c>
-      <c r="C28" s="49">
+      <c r="C28" s="37">
         <f>A28*'CVP Inputs'!$B$12</f>
         <v>2725000</v>
       </c>
-      <c r="D28" s="54">
+      <c r="D28" s="42">
         <f>'CVP Inputs'!$B$30</f>
         <v>469000</v>
       </c>
-      <c r="E28" s="49">
+      <c r="E28" s="37">
         <f t="shared" si="0"/>
         <v>3194000</v>
       </c>
-      <c r="F28" s="112">
+      <c r="F28" s="84">
         <f t="shared" si="1"/>
         <v>-2240610.1694915253</v>
       </c>
-      <c r="G28" s="49">
+      <c r="G28" s="37">
         <f>A28*'CVP Inputs'!$B$14</f>
         <v>-1771610.1694915253</v>
       </c>
-      <c r="H28" s="113" t="str">
+      <c r="H28" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="53">
+      <c r="A29" s="41">
         <v>60000</v>
       </c>
-      <c r="B29" s="49">
+      <c r="B29" s="37">
         <f>A29*'CVP Inputs'!$B$7</f>
         <v>1144067.7966101696</v>
       </c>
-      <c r="C29" s="49">
+      <c r="C29" s="37">
         <f>A29*'CVP Inputs'!$B$12</f>
         <v>3270000</v>
       </c>
-      <c r="D29" s="54">
+      <c r="D29" s="42">
         <f>'CVP Inputs'!$B$30</f>
         <v>469000</v>
       </c>
-      <c r="E29" s="49">
+      <c r="E29" s="37">
         <f t="shared" si="0"/>
         <v>3739000</v>
       </c>
-      <c r="F29" s="112">
+      <c r="F29" s="84">
         <f t="shared" si="1"/>
         <v>-2594932.2033898304</v>
       </c>
-      <c r="G29" s="49">
+      <c r="G29" s="37">
         <f>A29*'CVP Inputs'!$B$14</f>
         <v>-2125932.2033898304</v>
       </c>
-      <c r="H29" s="113" t="str">
+      <c r="H29" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="53">
+      <c r="A30" s="41">
         <v>70000</v>
       </c>
-      <c r="B30" s="49">
+      <c r="B30" s="37">
         <f>A30*'CVP Inputs'!$B$7</f>
         <v>1334745.7627118644</v>
       </c>
-      <c r="C30" s="49">
+      <c r="C30" s="37">
         <f>A30*'CVP Inputs'!$B$12</f>
         <v>3815000</v>
       </c>
-      <c r="D30" s="54">
+      <c r="D30" s="42">
         <f>'CVP Inputs'!$B$30</f>
         <v>469000</v>
       </c>
-      <c r="E30" s="49">
+      <c r="E30" s="37">
         <f t="shared" si="0"/>
         <v>4284000</v>
       </c>
-      <c r="F30" s="112">
+      <c r="F30" s="84">
         <f t="shared" si="1"/>
         <v>-2949254.2372881356</v>
       </c>
-      <c r="G30" s="49">
+      <c r="G30" s="37">
         <f>A30*'CVP Inputs'!$B$14</f>
         <v>-2480254.2372881356</v>
       </c>
-      <c r="H30" s="113" t="str">
+      <c r="H30" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="53">
+      <c r="A31" s="41">
         <v>80000</v>
       </c>
-      <c r="B31" s="49">
+      <c r="B31" s="37">
         <f>A31*'CVP Inputs'!$B$7</f>
         <v>1525423.7288135593</v>
       </c>
-      <c r="C31" s="49">
+      <c r="C31" s="37">
         <f>A31*'CVP Inputs'!$B$12</f>
         <v>4360000</v>
       </c>
-      <c r="D31" s="54">
+      <c r="D31" s="42">
         <f>'CVP Inputs'!$B$30</f>
         <v>469000</v>
       </c>
-      <c r="E31" s="49">
+      <c r="E31" s="37">
         <f t="shared" si="0"/>
         <v>4829000</v>
       </c>
-      <c r="F31" s="112">
+      <c r="F31" s="84">
         <f t="shared" si="1"/>
         <v>-3303576.2711864407</v>
       </c>
-      <c r="G31" s="49">
+      <c r="G31" s="37">
         <f>A31*'CVP Inputs'!$B$14</f>
         <v>-2834576.2711864403</v>
       </c>
-      <c r="H31" s="113" t="str">
+      <c r="H31" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="53">
+      <c r="A32" s="41">
         <v>90000</v>
       </c>
-      <c r="B32" s="49">
+      <c r="B32" s="37">
         <f>A32*'CVP Inputs'!$B$7</f>
         <v>1716101.6949152541</v>
       </c>
-      <c r="C32" s="49">
+      <c r="C32" s="37">
         <f>A32*'CVP Inputs'!$B$12</f>
         <v>4905000</v>
       </c>
-      <c r="D32" s="54">
+      <c r="D32" s="42">
         <f>'CVP Inputs'!$B$30</f>
         <v>469000</v>
       </c>
-      <c r="E32" s="49">
+      <c r="E32" s="37">
         <f t="shared" si="0"/>
         <v>5374000</v>
       </c>
-      <c r="F32" s="112">
+      <c r="F32" s="84">
         <f t="shared" si="1"/>
         <v>-3657898.3050847459</v>
       </c>
-      <c r="G32" s="49">
+      <c r="G32" s="37">
         <f>A32*'CVP Inputs'!$B$14</f>
         <v>-3188898.3050847454</v>
       </c>
-      <c r="H32" s="113" t="str">
+      <c r="H32" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="53">
+      <c r="A33" s="41">
         <v>100000</v>
       </c>
-      <c r="B33" s="49">
+      <c r="B33" s="37">
         <f>A33*'CVP Inputs'!$B$7</f>
         <v>1906779.6610169492</v>
       </c>
-      <c r="C33" s="49">
+      <c r="C33" s="37">
         <f>A33*'CVP Inputs'!$B$12</f>
         <v>5450000</v>
       </c>
-      <c r="D33" s="54">
+      <c r="D33" s="42">
         <f>'CVP Inputs'!$B$30</f>
         <v>469000</v>
       </c>
-      <c r="E33" s="49">
+      <c r="E33" s="37">
         <f t="shared" si="0"/>
         <v>5919000</v>
       </c>
-      <c r="F33" s="112">
+      <c r="F33" s="84">
         <f t="shared" si="1"/>
         <v>-4012220.3389830505</v>
       </c>
-      <c r="G33" s="49">
+      <c r="G33" s="37">
         <f>A33*'CVP Inputs'!$B$14</f>
         <v>-3543220.3389830505</v>
       </c>
-      <c r="H33" s="113" t="str">
+      <c r="H33" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="53">
+      <c r="A34" s="41">
         <v>200000</v>
       </c>
-      <c r="B34" s="49">
+      <c r="B34" s="37">
         <f>A34*'CVP Inputs'!$B$7</f>
         <v>3813559.3220338984</v>
       </c>
-      <c r="C34" s="49">
+      <c r="C34" s="37">
         <f>A34*'CVP Inputs'!$B$12</f>
         <v>10900000</v>
       </c>
-      <c r="D34" s="54">
+      <c r="D34" s="42">
         <f>'CVP Inputs'!$B$30</f>
         <v>469000</v>
       </c>
-      <c r="E34" s="49">
+      <c r="E34" s="37">
         <f t="shared" si="0"/>
         <v>11369000</v>
       </c>
-      <c r="F34" s="112">
+      <c r="F34" s="84">
         <f t="shared" si="1"/>
         <v>-7555440.6779661011</v>
       </c>
-      <c r="G34" s="49">
+      <c r="G34" s="37">
         <f>A34*'CVP Inputs'!$B$14</f>
         <v>-7086440.6779661011</v>
       </c>
-      <c r="H34" s="113" t="str">
+      <c r="H34" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="53">
+      <c r="A35" s="41">
         <v>300000</v>
       </c>
-      <c r="B35" s="49">
+      <c r="B35" s="37">
         <f>A35*'CVP Inputs'!$B$7</f>
         <v>5720338.9830508474</v>
       </c>
-      <c r="C35" s="49">
+      <c r="C35" s="37">
         <f>A35*'CVP Inputs'!$B$12</f>
         <v>16350000</v>
       </c>
-      <c r="D35" s="54">
+      <c r="D35" s="42">
         <f>'CVP Inputs'!$B$30</f>
         <v>469000</v>
       </c>
-      <c r="E35" s="49">
+      <c r="E35" s="37">
         <f t="shared" si="0"/>
         <v>16819000</v>
       </c>
-      <c r="F35" s="112">
+      <c r="F35" s="84">
         <f t="shared" si="1"/>
         <v>-11098661.016949153</v>
       </c>
-      <c r="G35" s="49">
+      <c r="G35" s="37">
         <f>A35*'CVP Inputs'!$B$14</f>
         <v>-10629661.016949151</v>
       </c>
-      <c r="H35" s="113" t="str">
+      <c r="H35" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="53">
+      <c r="A36" s="41">
         <v>400000</v>
       </c>
-      <c r="B36" s="49">
+      <c r="B36" s="37">
         <f>A36*'CVP Inputs'!$B$7</f>
         <v>7627118.6440677969</v>
       </c>
-      <c r="C36" s="49">
+      <c r="C36" s="37">
         <f>A36*'CVP Inputs'!$B$12</f>
         <v>21800000</v>
       </c>
-      <c r="D36" s="54">
+      <c r="D36" s="42">
         <f>'CVP Inputs'!$B$30</f>
         <v>469000</v>
       </c>
-      <c r="E36" s="49">
+      <c r="E36" s="37">
         <f t="shared" si="0"/>
         <v>22269000</v>
       </c>
-      <c r="F36" s="112">
+      <c r="F36" s="84">
         <f t="shared" si="1"/>
         <v>-14641881.355932202</v>
       </c>
-      <c r="G36" s="49">
+      <c r="G36" s="37">
         <f>A36*'CVP Inputs'!$B$14</f>
         <v>-14172881.355932202</v>
       </c>
-      <c r="H36" s="113" t="str">
+      <c r="H36" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="53">
+      <c r="A37" s="41">
         <v>500000</v>
       </c>
-      <c r="B37" s="49">
+      <c r="B37" s="37">
         <f>A37*'CVP Inputs'!$B$7</f>
         <v>9533898.3050847463</v>
       </c>
-      <c r="C37" s="49">
+      <c r="C37" s="37">
         <f>A37*'CVP Inputs'!$B$12</f>
         <v>27250000</v>
       </c>
-      <c r="D37" s="54">
+      <c r="D37" s="42">
         <f>'CVP Inputs'!$B$30</f>
         <v>469000</v>
       </c>
-      <c r="E37" s="49">
+      <c r="E37" s="37">
         <f t="shared" si="0"/>
         <v>27719000</v>
       </c>
-      <c r="F37" s="112">
+      <c r="F37" s="84">
         <f t="shared" si="1"/>
         <v>-18185101.694915254</v>
       </c>
-      <c r="G37" s="49">
+      <c r="G37" s="37">
         <f>A37*'CVP Inputs'!$B$14</f>
         <v>-17716101.694915254</v>
       </c>
-      <c r="H37" s="113" t="str">
+      <c r="H37" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="53">
+      <c r="A38" s="41">
         <v>600000</v>
       </c>
-      <c r="B38" s="49">
+      <c r="B38" s="37">
         <f>A38*'CVP Inputs'!$B$7</f>
         <v>11440677.966101695</v>
       </c>
-      <c r="C38" s="49">
+      <c r="C38" s="37">
         <f>A38*'CVP Inputs'!$B$12</f>
         <v>32700000</v>
       </c>
-      <c r="D38" s="54">
+      <c r="D38" s="42">
         <f>'CVP Inputs'!$B$30</f>
         <v>469000</v>
       </c>
-      <c r="E38" s="49">
+      <c r="E38" s="37">
         <f t="shared" si="0"/>
         <v>33169000</v>
       </c>
-      <c r="F38" s="112">
+      <c r="F38" s="84">
         <f t="shared" si="1"/>
         <v>-21728322.033898305</v>
       </c>
-      <c r="G38" s="49">
+      <c r="G38" s="37">
         <f>A38*'CVP Inputs'!$B$14</f>
         <v>-21259322.033898301</v>
       </c>
-      <c r="H38" s="113" t="str">
+      <c r="H38" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="53">
+      <c r="A39" s="41">
         <v>700000</v>
       </c>
-      <c r="B39" s="49">
+      <c r="B39" s="37">
         <f>A39*'CVP Inputs'!$B$7</f>
         <v>13347457.627118643</v>
       </c>
-      <c r="C39" s="49">
+      <c r="C39" s="37">
         <f>A39*'CVP Inputs'!$B$12</f>
         <v>38150000</v>
       </c>
-      <c r="D39" s="54">
+      <c r="D39" s="42">
         <f>'CVP Inputs'!$B$30</f>
         <v>469000</v>
       </c>
-      <c r="E39" s="49">
+      <c r="E39" s="37">
         <f t="shared" si="0"/>
         <v>38619000</v>
       </c>
-      <c r="F39" s="112">
+      <c r="F39" s="84">
         <f t="shared" si="1"/>
         <v>-25271542.372881357</v>
       </c>
-      <c r="G39" s="49">
+      <c r="G39" s="37">
         <f>A39*'CVP Inputs'!$B$14</f>
         <v>-24802542.372881353</v>
       </c>
-      <c r="H39" s="113" t="str">
+      <c r="H39" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="53">
+      <c r="A40" s="41">
         <v>1000000</v>
       </c>
-      <c r="B40" s="49">
+      <c r="B40" s="37">
         <f>A40*'CVP Inputs'!$B$7</f>
         <v>19067796.610169493</v>
       </c>
-      <c r="C40" s="49">
+      <c r="C40" s="37">
         <f>A40*'CVP Inputs'!$B$12</f>
         <v>54500000</v>
       </c>
-      <c r="D40" s="54">
+      <c r="D40" s="42">
         <f>'CVP Inputs'!$B$30</f>
         <v>469000</v>
       </c>
-      <c r="E40" s="49">
+      <c r="E40" s="37">
         <f t="shared" si="0"/>
         <v>54969000</v>
       </c>
-      <c r="F40" s="112">
+      <c r="F40" s="84">
         <f t="shared" si="1"/>
         <v>-35901203.389830507</v>
       </c>
-      <c r="G40" s="49">
+      <c r="G40" s="37">
         <f>A40*'CVP Inputs'!$B$14</f>
         <v>-35432203.389830507</v>
       </c>
-      <c r="H40" s="113" t="str">
+      <c r="H40" s="85" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="85" t="s">
+      <c r="A61" s="108" t="s">
         <v>145</v>
       </c>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="6" t="s">
+      <c r="B61" s="109"/>
+      <c r="C61" s="109"/>
+      <c r="D61" s="109"/>
+      <c r="E61" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
+      <c r="F61" s="110"/>
+      <c r="G61" s="110"/>
+      <c r="H61" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5731,460 +5730,460 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="117" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="101" t="s">
+      <c r="A3" s="115" t="s">
         <v>170</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E4" s="63" t="s">
+      <c r="E4" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="4" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="49">
+      <c r="B5" s="37">
         <f>'CVP Inputs'!B4</f>
         <v>150</v>
       </c>
-      <c r="C5" s="49">
+      <c r="C5" s="37">
         <f>'CVP Inputs'!B4</f>
         <v>150</v>
       </c>
-      <c r="D5" s="49">
+      <c r="D5" s="37">
         <f>'CVP Inputs'!B4*1.1</f>
         <v>165</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="37">
         <f>'CVP Inputs'!B4</f>
         <v>150</v>
       </c>
-      <c r="F5" s="49">
+      <c r="F5" s="37">
         <f>'CVP Inputs'!B4*0.9</f>
         <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="49">
+      <c r="B6" s="37">
         <f>'CVP Inputs'!B9</f>
         <v>50</v>
       </c>
-      <c r="C6" s="49">
+      <c r="C6" s="37">
         <f>'CVP Inputs'!B9*1.1</f>
         <v>55.000000000000007</v>
       </c>
-      <c r="D6" s="49">
+      <c r="D6" s="37">
         <f>'CVP Inputs'!B9</f>
         <v>50</v>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="37">
         <f>'CVP Inputs'!B9</f>
         <v>50</v>
       </c>
-      <c r="F6" s="49">
+      <c r="F6" s="37">
         <f>'CVP Inputs'!B9*1.1</f>
         <v>55.000000000000007</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="49">
+      <c r="B7" s="37">
         <f>'CVP Inputs'!B10</f>
         <v>3</v>
       </c>
-      <c r="C7" s="49">
+      <c r="C7" s="37">
         <f>'CVP Inputs'!B10*1.1</f>
         <v>3.3000000000000003</v>
       </c>
-      <c r="D7" s="49">
+      <c r="D7" s="37">
         <f>'CVP Inputs'!B10</f>
         <v>3</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="37">
         <f>'CVP Inputs'!B10</f>
         <v>3</v>
       </c>
-      <c r="F7" s="49">
+      <c r="F7" s="37">
         <f>'CVP Inputs'!B10*1.1</f>
         <v>3.3000000000000003</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="49">
+      <c r="B8" s="37">
         <f>'CVP Inputs'!B11</f>
         <v>1.5</v>
       </c>
-      <c r="C8" s="49">
+      <c r="C8" s="37">
         <f>'CVP Inputs'!B11*1.1</f>
         <v>1.6500000000000001</v>
       </c>
-      <c r="D8" s="49">
+      <c r="D8" s="37">
         <f>'CVP Inputs'!B11</f>
         <v>1.5</v>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="37">
         <f>'CVP Inputs'!B11</f>
         <v>1.5</v>
       </c>
-      <c r="F8" s="49">
+      <c r="F8" s="37">
         <f>'CVP Inputs'!B11*1.1</f>
         <v>1.6500000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="49">
+      <c r="B9" s="37">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="C9" s="49">
+      <c r="C9" s="37">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="D9" s="49">
+      <c r="D9" s="37">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="37">
         <f>'CVP Inputs'!B30*0.9</f>
         <v>422100</v>
       </c>
-      <c r="F9" s="49">
+      <c r="F9" s="37">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="114" t="s">
+      <c r="A10" s="119" t="s">
         <v>171</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
+      <c r="B10" s="105"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="49">
+      <c r="B11" s="37">
         <f>B5*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)</f>
         <v>19.067796610169491</v>
       </c>
-      <c r="C11" s="49">
+      <c r="C11" s="37">
         <f>C5*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)</f>
         <v>19.067796610169491</v>
       </c>
-      <c r="D11" s="49">
+      <c r="D11" s="37">
         <f>D5*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)</f>
         <v>20.974576271186443</v>
       </c>
-      <c r="E11" s="49">
+      <c r="E11" s="37">
         <f>E5*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)</f>
         <v>19.067796610169491</v>
       </c>
-      <c r="F11" s="49">
+      <c r="F11" s="37">
         <f>F5*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)</f>
         <v>17.161016949152543</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="49">
+      <c r="B12" s="37">
         <f>B6+B7+B8</f>
         <v>54.5</v>
       </c>
-      <c r="C12" s="49">
+      <c r="C12" s="37">
         <f>C6+C7+C8</f>
         <v>59.95</v>
       </c>
-      <c r="D12" s="49">
+      <c r="D12" s="37">
         <f>D6+D7+D8</f>
         <v>54.5</v>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="37">
         <f>E6+E7+E8</f>
         <v>54.5</v>
       </c>
-      <c r="F12" s="49">
+      <c r="F12" s="37">
         <f>F6+F7+F8</f>
         <v>59.95</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="40">
+      <c r="B13" s="28">
         <f>B11-B12</f>
         <v>-35.432203389830505</v>
       </c>
-      <c r="C13" s="40">
+      <c r="C13" s="28">
         <f>C11-C12</f>
         <v>-40.882203389830508</v>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="28">
         <f>D11-D12</f>
         <v>-33.525423728813557</v>
       </c>
-      <c r="E13" s="40">
+      <c r="E13" s="28">
         <f>E11-E12</f>
         <v>-35.432203389830505</v>
       </c>
-      <c r="F13" s="40">
+      <c r="F13" s="28">
         <f>F11-F12</f>
         <v>-42.788983050847463</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="49">
+      <c r="B14" s="37">
         <f>IFERROR(B13/B11,0)</f>
         <v>-1.858222222222222</v>
       </c>
-      <c r="C14" s="49">
+      <c r="C14" s="37">
         <f>IFERROR(C13/C11,0)</f>
         <v>-2.1440444444444444</v>
       </c>
-      <c r="D14" s="49">
+      <c r="D14" s="37">
         <f>IFERROR(D13/D11,0)</f>
         <v>-1.598383838383838</v>
       </c>
-      <c r="E14" s="49">
+      <c r="E14" s="37">
         <f>IFERROR(E13/E11,0)</f>
         <v>-1.858222222222222</v>
       </c>
-      <c r="F14" s="49">
+      <c r="F14" s="37">
         <f>IFERROR(F13/F11,0)</f>
         <v>-2.4933827160493829</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="115" t="s">
+      <c r="A15" s="120" t="s">
         <v>172</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
+      <c r="B15" s="104"/>
+      <c r="C15" s="104"/>
+      <c r="D15" s="104"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="43">
+      <c r="B16" s="31">
         <f>IFERROR(B9/B13,0)</f>
         <v>-13236.546280794069</v>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="31">
         <f>IFERROR(C9/C13,0)</f>
         <v>-11471.984411600091</v>
       </c>
-      <c r="D16" s="43">
+      <c r="D16" s="31">
         <f>IFERROR(D9/D13,0)</f>
         <v>-13989.38321536906</v>
       </c>
-      <c r="E16" s="43">
+      <c r="E16" s="31">
         <f>IFERROR(E9/E13,0)</f>
         <v>-11912.891652714663</v>
       </c>
-      <c r="F16" s="43">
+      <c r="F16" s="31">
         <f>IFERROR(F9/F13,0)</f>
         <v>-10960.765284902258</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="44">
+      <c r="B17" s="32">
         <f>IFERROR(B16/30,0)</f>
         <v>-441.2182093598023</v>
       </c>
-      <c r="C17" s="44">
+      <c r="C17" s="32">
         <f>IFERROR(C16/30,0)</f>
         <v>-382.39948038666972</v>
       </c>
-      <c r="D17" s="44">
+      <c r="D17" s="32">
         <f>IFERROR(D16/30,0)</f>
         <v>-466.31277384563532</v>
       </c>
-      <c r="E17" s="44">
+      <c r="E17" s="32">
         <f>IFERROR(E16/30,0)</f>
         <v>-397.09638842382208</v>
       </c>
-      <c r="F17" s="44">
+      <c r="F17" s="32">
         <f>IFERROR(F16/30,0)</f>
         <v>-365.35884283007528</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="40">
+      <c r="B18" s="28">
         <f>B16*B11</f>
         <v>-252391.77230327675</v>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="28">
         <f>C16*C11</f>
         <v>-218745.46547542547</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="28">
         <f>D16*D11</f>
         <v>-293421.38523761381</v>
       </c>
-      <c r="E18" s="40">
+      <c r="E18" s="28">
         <f>E16*E11</f>
         <v>-227152.59507294907</v>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="28">
         <f>F16*F11</f>
         <v>-188097.87882989045</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="50" t="s">
+      <c r="A19" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="B19" s="117" t="s">
+      <c r="B19" s="87" t="s">
         <v>173</v>
       </c>
-      <c r="C19" s="64">
+      <c r="C19" s="52">
         <f>C16-B16</f>
         <v>1764.5618691939781</v>
       </c>
-      <c r="D19" s="64">
+      <c r="D19" s="52">
         <f>D16-B16</f>
         <v>-752.83693457499066</v>
       </c>
-      <c r="E19" s="64">
+      <c r="E19" s="52">
         <f>E16-B16</f>
         <v>1323.6546280794064</v>
       </c>
-      <c r="F19" s="64">
+      <c r="F19" s="52">
         <f>F16-B16</f>
         <v>2275.7809958918115</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="B20" s="116" t="s">
+      <c r="B20" s="86" t="s">
         <v>173</v>
       </c>
-      <c r="C20" s="65">
+      <c r="C20" s="53">
         <f>IFERROR((C16-B16)/B16,0)</f>
         <v>-0.13330984017744249</v>
       </c>
-      <c r="D20" s="65">
+      <c r="D20" s="53">
         <f>IFERROR((D16-B16)/B16,0)</f>
         <v>5.6875631951466075E-2</v>
       </c>
-      <c r="E20" s="65">
+      <c r="E20" s="53">
         <f>IFERROR((E16-B16)/B16,0)</f>
         <v>-9.9999999999999964E-2</v>
       </c>
-      <c r="F20" s="65">
+      <c r="F20" s="53">
         <f>IFERROR((F16-B16)/B16,0)</f>
         <v>-0.17193163137985007</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="97" t="s">
+      <c r="A22" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
+      <c r="B22" s="107"/>
+      <c r="C22" s="107"/>
+      <c r="D22" s="107"/>
+      <c r="E22" s="107"/>
+      <c r="F22" s="107"/>
     </row>
     <row r="23" spans="1:6" ht="138" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="66"/>
-      <c r="B23" s="67" t="s">
+      <c r="A23" s="54"/>
+      <c r="B23" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="C23" s="67" t="s">
+      <c r="C23" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="D23" s="67" t="s">
+      <c r="D23" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="E23" s="67" t="s">
+      <c r="E23" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="F23" s="67" t="s">
+      <c r="F23" s="55" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="6" t="s">
+      <c r="B25" s="109"/>
+      <c r="C25" s="109"/>
+      <c r="D25" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -6216,446 +6215,445 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="94" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
     </row>
     <row r="2" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="98" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
     </row>
     <row r="3" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="96" t="s">
         <v>118</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
     </row>
     <row r="4" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="121" t="s">
+      <c r="A4" s="88" t="s">
         <v>176</v>
       </c>
-      <c r="B4" s="48">
+      <c r="B4" s="36">
         <v>5980</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="88" t="s">
+      <c r="D4" s="91" t="s">
         <v>119</v>
       </c>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="69">
+      <c r="B5" s="57">
         <f>'CVP Inputs'!B30</f>
         <v>469000</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="16" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="70">
+      <c r="B6" s="58">
         <f>'CVP Inputs'!B12</f>
         <v>54.5</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="16" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B7" s="71">
+      <c r="B7" s="59">
         <f>IFERROR('CVP Inputs'!B30/B4,0)</f>
         <v>78.42809364548495</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="D7" s="86" t="s">
+      <c r="D7" s="89" t="s">
         <v>124</v>
       </c>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
+      <c r="E7" s="90"/>
+      <c r="F7" s="90"/>
+      <c r="G7" s="90"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="90"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B8" s="71">
+      <c r="B8" s="59">
         <f>B7+'CVP Inputs'!B12</f>
         <v>132.92809364548495</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="D8" s="86" t="s">
+      <c r="D8" s="89" t="s">
         <v>126</v>
       </c>
-      <c r="E8" s="87"/>
-      <c r="F8" s="87"/>
-      <c r="G8" s="87"/>
-      <c r="H8" s="87"/>
-      <c r="I8" s="87"/>
+      <c r="E8" s="90"/>
+      <c r="F8" s="90"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="90"/>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B9" s="71">
+      <c r="B9" s="59">
         <f>IFERROR(B8*(1+'CVP Inputs'!B6)/'CVP Inputs'!B5,0)</f>
         <v>1045.7010033444815</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="86" t="s">
+      <c r="D9" s="89" t="s">
         <v>128</v>
       </c>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="87"/>
+      <c r="E9" s="90"/>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="90"/>
+      <c r="I9" s="90"/>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="92" t="s">
+      <c r="A11" s="97" t="s">
         <v>129</v>
       </c>
-      <c r="B11" s="92"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="92"/>
-      <c r="H11" s="92"/>
-      <c r="I11" s="92"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="97"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="97"/>
+      <c r="F11" s="97"/>
+      <c r="G11" s="97"/>
+      <c r="H11" s="97"/>
+      <c r="I11" s="97"/>
     </row>
     <row r="12" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="68" t="s">
+      <c r="A12" s="56" t="s">
         <v>177</v>
       </c>
-      <c r="B12" s="39">
+      <c r="B12" s="27">
         <v>100</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="88" t="s">
+      <c r="D12" s="91" t="s">
         <v>130</v>
       </c>
-      <c r="E12" s="89"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="89"/>
-      <c r="H12" s="89"/>
-      <c r="I12" s="89"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="92"/>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B13" s="72">
+      <c r="B13" s="60">
         <f>IFERROR(('CVP Inputs'!B30+B12)/'CVP Inputs'!B14,0)</f>
         <v>-13239.368572111936</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="86" t="s">
+      <c r="D13" s="89" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="87"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="87"/>
-      <c r="I13" s="87"/>
+      <c r="E13" s="90"/>
+      <c r="F13" s="90"/>
+      <c r="G13" s="90"/>
+      <c r="H13" s="90"/>
+      <c r="I13" s="90"/>
     </row>
     <row r="14" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="73">
+      <c r="B14" s="61">
         <f>IFERROR(B13/30,0)</f>
         <v>-441.31228573706454</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="86" t="s">
+      <c r="D14" s="89" t="s">
         <v>135</v>
       </c>
-      <c r="E14" s="87"/>
-      <c r="F14" s="87"/>
-      <c r="G14" s="87"/>
-      <c r="H14" s="87"/>
-      <c r="I14" s="87"/>
+      <c r="E14" s="90"/>
+      <c r="F14" s="90"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="90"/>
+      <c r="I14" s="90"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="74">
+      <c r="B15" s="62">
         <f>B13*'CVP Inputs'!B7</f>
         <v>-252445.58718010047</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="86" t="s">
+      <c r="D15" s="89" t="s">
         <v>137</v>
       </c>
-      <c r="E15" s="87"/>
-      <c r="F15" s="87"/>
-      <c r="G15" s="87"/>
-      <c r="H15" s="87"/>
-      <c r="I15" s="87"/>
+      <c r="E15" s="90"/>
+      <c r="F15" s="90"/>
+      <c r="G15" s="90"/>
+      <c r="H15" s="90"/>
+      <c r="I15" s="90"/>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="91" t="s">
+      <c r="A17" s="93" t="s">
         <v>138</v>
       </c>
-      <c r="B17" s="91"/>
-      <c r="C17" s="91"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="91"/>
-      <c r="F17" s="91"/>
-      <c r="G17" s="91"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="93"/>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="75" t="s">
+      <c r="A18" s="63" t="s">
         <v>139</v>
       </c>
-      <c r="B18" s="76">
+      <c r="B18" s="64">
         <v>4680</v>
       </c>
-      <c r="C18" s="76">
+      <c r="C18" s="64">
         <v>5980</v>
       </c>
-      <c r="D18" s="76">
+      <c r="D18" s="64">
         <v>8000</v>
       </c>
-      <c r="E18" s="76">
+      <c r="E18" s="64">
         <v>10000</v>
       </c>
-      <c r="F18" s="76">
+      <c r="F18" s="64">
         <v>12000</v>
       </c>
-      <c r="G18" s="76">
+      <c r="G18" s="64">
         <v>15000</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="77" t="s">
+      <c r="A19" s="65" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="78">
+      <c r="B19" s="66">
         <f>B18*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-45-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-611422.71186440671</v>
       </c>
-      <c r="C19" s="78">
+      <c r="C19" s="66">
         <f>C18*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-45-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-650984.57627118647</v>
       </c>
-      <c r="D19" s="78">
+      <c r="D19" s="66">
         <f>D18*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-45-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-712457.62711864407</v>
       </c>
-      <c r="E19" s="78">
+      <c r="E19" s="66">
         <f>E18*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-45-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-773322.03389830515</v>
       </c>
-      <c r="F19" s="78">
+      <c r="F19" s="66">
         <f>F18*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-45-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-834186.44067796611</v>
       </c>
-      <c r="G19" s="78">
+      <c r="G19" s="66">
         <f>15000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-45-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-925483.05084745761</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="77" t="s">
+      <c r="A20" s="65" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="78">
+      <c r="B20" s="66">
         <f>4680*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-48-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-625462.71186440671</v>
       </c>
-      <c r="C20" s="78">
+      <c r="C20" s="66">
         <f>5980*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-48-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-668924.57627118635</v>
       </c>
-      <c r="D20" s="78">
+      <c r="D20" s="66">
         <f>8000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-48-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-736457.62711864407</v>
       </c>
-      <c r="E20" s="78">
+      <c r="E20" s="66">
         <f>10000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-48-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-803322.03389830503</v>
       </c>
-      <c r="F20" s="78">
+      <c r="F20" s="66">
         <f>12000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-48-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-870186.44067796599</v>
       </c>
-      <c r="G20" s="78">
+      <c r="G20" s="66">
         <f>15000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-48-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-970483.05084745761</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="77" t="s">
+      <c r="A21" s="65" t="s">
         <v>142</v>
       </c>
-      <c r="B21" s="79">
+      <c r="B21" s="67">
         <f>4680*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-50-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-634822.71186440671</v>
       </c>
-      <c r="C21" s="79">
+      <c r="C21" s="67">
         <f>5980*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-50-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-680884.57627118635</v>
       </c>
-      <c r="D21" s="79">
+      <c r="D21" s="67">
         <f>8000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-50-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-752457.62711864407</v>
       </c>
-      <c r="E21" s="79">
+      <c r="E21" s="67">
         <f>10000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-50-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-823322.03389830503</v>
       </c>
-      <c r="F21" s="79">
+      <c r="F21" s="67">
         <f>12000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-50-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-894186.44067796599</v>
       </c>
-      <c r="G21" s="79">
+      <c r="G21" s="67">
         <f>15000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-50-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-1000483.0508474576</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="77" t="s">
+      <c r="A22" s="65" t="s">
         <v>143</v>
       </c>
-      <c r="B22" s="80">
+      <c r="B22" s="68">
         <f>4680*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-52-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-644182.71186440671</v>
       </c>
-      <c r="C22" s="80">
+      <c r="C22" s="68">
         <f>5980*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-52-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-692844.57627118635</v>
       </c>
-      <c r="D22" s="80">
+      <c r="D22" s="68">
         <f>8000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-52-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-768457.62711864407</v>
       </c>
-      <c r="E22" s="80">
+      <c r="E22" s="68">
         <f>10000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-52-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-843322.03389830503</v>
       </c>
-      <c r="F22" s="80">
+      <c r="F22" s="68">
         <f>12000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-52-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-918186.44067796599</v>
       </c>
-      <c r="G22" s="80">
+      <c r="G22" s="68">
         <f>15000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-52-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-1030483.0508474576</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="77" t="s">
+      <c r="A23" s="65" t="s">
         <v>144</v>
       </c>
-      <c r="B23" s="80">
+      <c r="B23" s="68">
         <f>4680*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-55-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-658222.71186440671</v>
       </c>
-      <c r="C23" s="80">
+      <c r="C23" s="68">
         <f>5980*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-55-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-710784.57627118635</v>
       </c>
-      <c r="D23" s="80">
+      <c r="D23" s="68">
         <f>8000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-55-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-792457.62711864407</v>
       </c>
-      <c r="E23" s="80">
+      <c r="E23" s="68">
         <f>10000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-55-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-873322.03389830503</v>
       </c>
-      <c r="F23" s="80">
+      <c r="F23" s="68">
         <f>12000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-55-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-954186.44067796599</v>
       </c>
-      <c r="G23" s="80">
+      <c r="G23" s="68">
         <f>15000*(150*'CVP Inputs'!B5/(1+'CVP Inputs'!B6)-55-'CVP Inputs'!B10-'CVP Inputs'!B11)-'CVP Inputs'!B30</f>
         <v>-1075483.0508474577</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="82" t="s">
+      <c r="A25" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="82"/>
-      <c r="C25" s="82"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="82"/>
-      <c r="F25" s="82"/>
-      <c r="G25" s="82" t="s">
+      <c r="B25" s="69"/>
+      <c r="C25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="69" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="D15:I15"/>
     <mergeCell ref="D14:I14"/>
     <mergeCell ref="D13:I13"/>
     <mergeCell ref="D12:I12"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
